--- a/output/yearly_total_coral_cover_iteration_40_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_40_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.282689145787709</v>
+        <v>1.255592909150497</v>
       </c>
       <c r="C3" t="n">
-        <v>4.629968206430219</v>
+        <v>4.640836153516231</v>
       </c>
       <c r="D3" t="n">
-        <v>6.055866628934399</v>
+        <v>6.116793891459957</v>
       </c>
       <c r="E3" t="n">
-        <v>11.96852398115233</v>
+        <v>12.01322295412668</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.454157963603096</v>
+        <v>1.380224691709394</v>
       </c>
       <c r="C4" t="n">
-        <v>5.115521115543468</v>
+        <v>5.168897854661621</v>
       </c>
       <c r="D4" t="n">
-        <v>6.316835361027237</v>
+        <v>6.351990843991149</v>
       </c>
       <c r="E4" t="n">
-        <v>12.8865144401738</v>
+        <v>12.90111339036216</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.684824868336632</v>
+        <v>1.544462652113945</v>
       </c>
       <c r="C5" t="n">
-        <v>5.698926217149759</v>
+        <v>5.825566058549449</v>
       </c>
       <c r="D5" t="n">
-        <v>6.567962107708617</v>
+        <v>6.684345863431589</v>
       </c>
       <c r="E5" t="n">
-        <v>13.95171319319501</v>
+        <v>14.05437457409498</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.938040773309</v>
+        <v>1.745978242825893</v>
       </c>
       <c r="C6" t="n">
-        <v>6.388987217796047</v>
+        <v>6.617338738196879</v>
       </c>
       <c r="D6" t="n">
-        <v>6.925443316638392</v>
+        <v>6.979369316244164</v>
       </c>
       <c r="E6" t="n">
-        <v>15.25247130774344</v>
+        <v>15.34268629726694</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.218356921988054</v>
+        <v>1.982350355030093</v>
       </c>
       <c r="C7" t="n">
-        <v>7.172608681849303</v>
+        <v>7.526701181725823</v>
       </c>
       <c r="D7" t="n">
-        <v>7.223834642449982</v>
+        <v>7.392882714100181</v>
       </c>
       <c r="E7" t="n">
-        <v>16.61480024628734</v>
+        <v>16.9019342508561</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.402193854194087</v>
+        <v>1.236177241961236</v>
       </c>
       <c r="C8" t="n">
-        <v>4.757124753272384</v>
+        <v>5.129850798065118</v>
       </c>
       <c r="D8" t="n">
-        <v>5.53135525638524</v>
+        <v>5.60125831974737</v>
       </c>
       <c r="E8" t="n">
-        <v>11.69067386385171</v>
+        <v>11.96728635977372</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.782761968739177</v>
+        <v>1.569369204685816</v>
       </c>
       <c r="C9" t="n">
-        <v>5.731317938863186</v>
+        <v>6.261997555220265</v>
       </c>
       <c r="D9" t="n">
-        <v>6.033869865285677</v>
+        <v>6.078451404351775</v>
       </c>
       <c r="E9" t="n">
-        <v>13.54794977288804</v>
+        <v>13.90981816425785</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.190122622147361</v>
+        <v>1.921797437470981</v>
       </c>
       <c r="C10" t="n">
-        <v>6.854456166527415</v>
+        <v>7.562192912833798</v>
       </c>
       <c r="D10" t="n">
-        <v>6.59979951540459</v>
+        <v>6.550722302847407</v>
       </c>
       <c r="E10" t="n">
-        <v>15.64437830407937</v>
+        <v>16.03471265315219</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.596354231722626</v>
+        <v>2.274352022405662</v>
       </c>
       <c r="C11" t="n">
-        <v>8.128896233566351</v>
+        <v>8.988564979326648</v>
       </c>
       <c r="D11" t="n">
-        <v>7.199124295085056</v>
+        <v>6.984257181098608</v>
       </c>
       <c r="E11" t="n">
-        <v>17.92437476037403</v>
+        <v>18.24717418283092</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.005389628830305</v>
+        <v>2.657942192088644</v>
       </c>
       <c r="C12" t="n">
-        <v>9.538226547263573</v>
+        <v>10.46164362974011</v>
       </c>
       <c r="D12" t="n">
-        <v>7.709479095307517</v>
+        <v>7.471752789369686</v>
       </c>
       <c r="E12" t="n">
-        <v>20.2530952714014</v>
+        <v>20.59133861119844</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.413338992052625</v>
+        <v>3.033956821615825</v>
       </c>
       <c r="C13" t="n">
-        <v>10.99821485882519</v>
+        <v>11.94599952281956</v>
       </c>
       <c r="D13" t="n">
-        <v>8.295266675891069</v>
+        <v>7.906967836102988</v>
       </c>
       <c r="E13" t="n">
-        <v>22.70682052676889</v>
+        <v>22.88692418053837</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.973528870031023</v>
+        <v>1.748286494245677</v>
       </c>
       <c r="C14" t="n">
-        <v>7.838047868734558</v>
+        <v>8.369703520492374</v>
       </c>
       <c r="D14" t="n">
-        <v>6.349688896665266</v>
+        <v>6.001305906336242</v>
       </c>
       <c r="E14" t="n">
-        <v>16.16126563543085</v>
+        <v>16.11929592107429</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2.034632847143345</v>
+        <v>1.823458915959856</v>
       </c>
       <c r="C15" t="n">
-        <v>8.452268502419532</v>
+        <v>8.934964396166562</v>
       </c>
       <c r="D15" t="n">
-        <v>6.421081589718093</v>
+        <v>5.989897998012895</v>
       </c>
       <c r="E15" t="n">
-        <v>16.90798293928097</v>
+        <v>16.74832131013931</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.373090368182432</v>
+        <v>2.156222300314313</v>
       </c>
       <c r="C16" t="n">
-        <v>10.0296229038788</v>
+        <v>10.48527164837383</v>
       </c>
       <c r="D16" t="n">
-        <v>6.961995122326958</v>
+        <v>6.418764665136071</v>
       </c>
       <c r="E16" t="n">
-        <v>19.36470839438819</v>
+        <v>19.06025861382421</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.905071602613894</v>
+        <v>1.76372938563348</v>
       </c>
       <c r="C17" t="n">
-        <v>9.30174533847317</v>
+        <v>9.586648522245595</v>
       </c>
       <c r="D17" t="n">
-        <v>6.514180724511819</v>
+        <v>5.945395374579387</v>
       </c>
       <c r="E17" t="n">
-        <v>17.72099766559888</v>
+        <v>17.29577328245846</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.184722436168597</v>
+        <v>2.044666308680747</v>
       </c>
       <c r="C18" t="n">
-        <v>10.88670828464035</v>
+        <v>11.14019554187687</v>
       </c>
       <c r="D18" t="n">
-        <v>6.98407462819547</v>
+        <v>6.390048544786851</v>
       </c>
       <c r="E18" t="n">
-        <v>20.05550534900442</v>
+        <v>19.57491039534447</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.20167721902094</v>
+        <v>2.077515586864846</v>
       </c>
       <c r="C19" t="n">
-        <v>11.69082837675778</v>
+        <v>11.85640012707901</v>
       </c>
       <c r="D19" t="n">
-        <v>7.136117895152172</v>
+        <v>6.473320385061066</v>
       </c>
       <c r="E19" t="n">
-        <v>21.0286234909309</v>
+        <v>20.40723609900492</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.457255598867512</v>
+        <v>2.344973113932804</v>
       </c>
       <c r="C20" t="n">
-        <v>13.52162094806836</v>
+        <v>13.57063961094141</v>
       </c>
       <c r="D20" t="n">
-        <v>7.598521063852421</v>
+        <v>6.900164651913494</v>
       </c>
       <c r="E20" t="n">
-        <v>23.57739761078829</v>
+        <v>22.8157773767877</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.468400041241954</v>
+        <v>1.409534448895316</v>
       </c>
       <c r="C21" t="n">
-        <v>10.05815249216421</v>
+        <v>9.945084609066104</v>
       </c>
       <c r="D21" t="n">
-        <v>6.3621570925092</v>
+        <v>5.736881979674407</v>
       </c>
       <c r="E21" t="n">
-        <v>17.88870962591536</v>
+        <v>17.09150103763583</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_40_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_40_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.255592909150497</v>
+        <v>1.253796310851725</v>
       </c>
       <c r="C3" t="n">
-        <v>4.640836153516231</v>
+        <v>4.624755126120668</v>
       </c>
       <c r="D3" t="n">
-        <v>6.116793891459957</v>
+        <v>6.06319046680808</v>
       </c>
       <c r="E3" t="n">
-        <v>12.01322295412668</v>
+        <v>11.94174190378047</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.380224691709394</v>
+        <v>1.385057345212512</v>
       </c>
       <c r="C4" t="n">
-        <v>5.168897854661621</v>
+        <v>5.132087659860622</v>
       </c>
       <c r="D4" t="n">
-        <v>6.351990843991149</v>
+        <v>6.27769362153084</v>
       </c>
       <c r="E4" t="n">
-        <v>12.90111339036216</v>
+        <v>12.79483862660397</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.544462652113945</v>
+        <v>1.573497783272001</v>
       </c>
       <c r="C5" t="n">
-        <v>5.825566058549449</v>
+        <v>5.769316763101155</v>
       </c>
       <c r="D5" t="n">
-        <v>6.684345863431589</v>
+        <v>6.59596633950764</v>
       </c>
       <c r="E5" t="n">
-        <v>14.05437457409498</v>
+        <v>13.9387808858808</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.745978242825893</v>
+        <v>1.788645821882334</v>
       </c>
       <c r="C6" t="n">
-        <v>6.617338738196879</v>
+        <v>6.528393494563536</v>
       </c>
       <c r="D6" t="n">
-        <v>6.979369316244164</v>
+        <v>6.973203639720865</v>
       </c>
       <c r="E6" t="n">
-        <v>15.34268629726694</v>
+        <v>15.29024295616673</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.982350355030093</v>
+        <v>2.022234895038157</v>
       </c>
       <c r="C7" t="n">
-        <v>7.526701181725823</v>
+        <v>7.394780005631069</v>
       </c>
       <c r="D7" t="n">
-        <v>7.392882714100181</v>
+        <v>7.322174624652702</v>
       </c>
       <c r="E7" t="n">
-        <v>16.9019342508561</v>
+        <v>16.73918952532193</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.236177241961236</v>
+        <v>1.242423123783633</v>
       </c>
       <c r="C8" t="n">
-        <v>5.129850798065118</v>
+        <v>5.04559110161331</v>
       </c>
       <c r="D8" t="n">
-        <v>5.60125831974737</v>
+        <v>5.584250990924062</v>
       </c>
       <c r="E8" t="n">
-        <v>11.96728635977372</v>
+        <v>11.872265216321</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.569369204685816</v>
+        <v>1.55928848559519</v>
       </c>
       <c r="C9" t="n">
-        <v>6.261997555220265</v>
+        <v>6.211710560176919</v>
       </c>
       <c r="D9" t="n">
-        <v>6.078451404351775</v>
+        <v>6.084885458794601</v>
       </c>
       <c r="E9" t="n">
-        <v>13.90981816425785</v>
+        <v>13.85588450456671</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.921797437470981</v>
+        <v>1.89652501376601</v>
       </c>
       <c r="C10" t="n">
-        <v>7.562192912833798</v>
+        <v>7.544140949597931</v>
       </c>
       <c r="D10" t="n">
-        <v>6.550722302847407</v>
+        <v>6.601226909626447</v>
       </c>
       <c r="E10" t="n">
-        <v>16.03471265315219</v>
+        <v>16.04189287299039</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.274352022405662</v>
+        <v>2.245025425285161</v>
       </c>
       <c r="C11" t="n">
-        <v>8.988564979326648</v>
+        <v>9.037434778153242</v>
       </c>
       <c r="D11" t="n">
-        <v>6.984257181098608</v>
+        <v>7.096177586197572</v>
       </c>
       <c r="E11" t="n">
-        <v>18.24717418283092</v>
+        <v>18.37863778963598</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.657942192088644</v>
+        <v>2.599919491750369</v>
       </c>
       <c r="C12" t="n">
-        <v>10.46164362974011</v>
+        <v>10.63906362815155</v>
       </c>
       <c r="D12" t="n">
-        <v>7.471752789369686</v>
+        <v>7.62278280835928</v>
       </c>
       <c r="E12" t="n">
-        <v>20.59133861119844</v>
+        <v>20.8617659282612</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.033956821615825</v>
+        <v>2.941926338698668</v>
       </c>
       <c r="C13" t="n">
-        <v>11.94599952281956</v>
+        <v>12.26586399735429</v>
       </c>
       <c r="D13" t="n">
-        <v>7.906967836102988</v>
+        <v>8.112249656309492</v>
       </c>
       <c r="E13" t="n">
-        <v>22.88692418053837</v>
+        <v>23.32003999236245</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.748286494245677</v>
+        <v>1.696381493122149</v>
       </c>
       <c r="C14" t="n">
-        <v>8.369703520492374</v>
+        <v>8.61117418582892</v>
       </c>
       <c r="D14" t="n">
-        <v>6.001305906336242</v>
+        <v>6.171256251418408</v>
       </c>
       <c r="E14" t="n">
-        <v>16.11929592107429</v>
+        <v>16.47881193036948</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.823458915959856</v>
+        <v>1.742376373066112</v>
       </c>
       <c r="C15" t="n">
-        <v>8.934964396166562</v>
+        <v>9.342389693428988</v>
       </c>
       <c r="D15" t="n">
-        <v>5.989897998012895</v>
+        <v>6.199550220254801</v>
       </c>
       <c r="E15" t="n">
-        <v>16.74832131013931</v>
+        <v>17.2843162867499</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.156222300314313</v>
+        <v>2.040150269241212</v>
       </c>
       <c r="C16" t="n">
-        <v>10.48527164837383</v>
+        <v>11.09925666260978</v>
       </c>
       <c r="D16" t="n">
-        <v>6.418764665136071</v>
+        <v>6.657476619423683</v>
       </c>
       <c r="E16" t="n">
-        <v>19.06025861382421</v>
+        <v>19.79688355127468</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.76372938563348</v>
+        <v>1.649993914096487</v>
       </c>
       <c r="C17" t="n">
-        <v>9.586648522245595</v>
+        <v>10.29493040347445</v>
       </c>
       <c r="D17" t="n">
-        <v>5.945395374579387</v>
+        <v>6.174073867329596</v>
       </c>
       <c r="E17" t="n">
-        <v>17.29577328245846</v>
+        <v>18.11899818490054</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.044666308680747</v>
+        <v>1.892524866953619</v>
       </c>
       <c r="C18" t="n">
-        <v>11.14019554187687</v>
+        <v>12.08751335413575</v>
       </c>
       <c r="D18" t="n">
-        <v>6.390048544786851</v>
+        <v>6.578200492305752</v>
       </c>
       <c r="E18" t="n">
-        <v>19.57491039534447</v>
+        <v>20.55823871339512</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.077515586864846</v>
+        <v>1.90624969985899</v>
       </c>
       <c r="C19" t="n">
-        <v>11.85640012707901</v>
+        <v>12.99559071065588</v>
       </c>
       <c r="D19" t="n">
-        <v>6.473320385061066</v>
+        <v>6.657142825204239</v>
       </c>
       <c r="E19" t="n">
-        <v>20.40723609900492</v>
+        <v>21.55898323571911</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.344973113932804</v>
+        <v>2.122636711352029</v>
       </c>
       <c r="C20" t="n">
-        <v>13.57063961094141</v>
+        <v>15.01217903499517</v>
       </c>
       <c r="D20" t="n">
-        <v>6.900164651913494</v>
+        <v>7.10698944076717</v>
       </c>
       <c r="E20" t="n">
-        <v>22.8157773767877</v>
+        <v>24.24180518711437</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.409534448895316</v>
+        <v>1.262949699174224</v>
       </c>
       <c r="C21" t="n">
-        <v>9.945084609066104</v>
+        <v>11.09820619256624</v>
       </c>
       <c r="D21" t="n">
-        <v>5.736881979674407</v>
+        <v>5.932338130112904</v>
       </c>
       <c r="E21" t="n">
-        <v>17.09150103763583</v>
+        <v>18.29349402185337</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_40_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_40_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.253796310851725</v>
+        <v>2.591332404720028</v>
       </c>
       <c r="C3" t="n">
-        <v>4.624755126120668</v>
+        <v>7.724859345268448</v>
       </c>
       <c r="D3" t="n">
-        <v>6.06319046680808</v>
+        <v>8.179909859364804</v>
       </c>
       <c r="E3" t="n">
-        <v>11.94174190378047</v>
+        <v>18.49610160935328</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.385057345212512</v>
+        <v>1.076781212985793</v>
       </c>
       <c r="C4" t="n">
-        <v>5.132087659860622</v>
+        <v>4.508628943336777</v>
       </c>
       <c r="D4" t="n">
-        <v>6.27769362153084</v>
+        <v>5.824974223240998</v>
       </c>
       <c r="E4" t="n">
-        <v>12.79483862660397</v>
+        <v>11.41038437956357</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.573497783272001</v>
+        <v>1.176834994503245</v>
       </c>
       <c r="C5" t="n">
-        <v>5.769316763101155</v>
+        <v>5.153007395844527</v>
       </c>
       <c r="D5" t="n">
-        <v>6.59596633950764</v>
+        <v>6.114139242065808</v>
       </c>
       <c r="E5" t="n">
-        <v>13.9387808858808</v>
+        <v>12.44398163241358</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.788645821882334</v>
+        <v>1.289604047360613</v>
       </c>
       <c r="C6" t="n">
-        <v>6.528393494563536</v>
+        <v>5.958959254787803</v>
       </c>
       <c r="D6" t="n">
-        <v>6.973203639720865</v>
+        <v>6.450082399904226</v>
       </c>
       <c r="E6" t="n">
-        <v>15.29024295616673</v>
+        <v>13.69864570205264</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.022234895038157</v>
+        <v>1.405154370109801</v>
       </c>
       <c r="C7" t="n">
-        <v>7.394780005631069</v>
+        <v>6.939814269413058</v>
       </c>
       <c r="D7" t="n">
-        <v>7.322174624652702</v>
+        <v>6.768309939004423</v>
       </c>
       <c r="E7" t="n">
-        <v>16.73918952532193</v>
+        <v>15.11327857852728</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.242423123783633</v>
+        <v>1.526681765127065</v>
       </c>
       <c r="C8" t="n">
-        <v>5.04559110161331</v>
+        <v>8.045785278980468</v>
       </c>
       <c r="D8" t="n">
-        <v>5.584250990924062</v>
+        <v>7.114277758142197</v>
       </c>
       <c r="E8" t="n">
-        <v>11.872265216321</v>
+        <v>16.68674480224973</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.55928848559519</v>
+        <v>1.655158939429733</v>
       </c>
       <c r="C9" t="n">
-        <v>6.211710560176919</v>
+        <v>9.252640771855374</v>
       </c>
       <c r="D9" t="n">
-        <v>6.084885458794601</v>
+        <v>7.465017696016032</v>
       </c>
       <c r="E9" t="n">
-        <v>13.85588450456671</v>
+        <v>18.37281740730114</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.89652501376601</v>
+        <v>1.041035448106275</v>
       </c>
       <c r="C10" t="n">
-        <v>7.544140949597931</v>
+        <v>6.806584460744688</v>
       </c>
       <c r="D10" t="n">
-        <v>6.601226909626447</v>
+        <v>5.856527572390966</v>
       </c>
       <c r="E10" t="n">
-        <v>16.04189287299039</v>
+        <v>13.70414748124193</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.245025425285161</v>
+        <v>0.9804812497083319</v>
       </c>
       <c r="C11" t="n">
-        <v>9.037434778153242</v>
+        <v>7.159895824549031</v>
       </c>
       <c r="D11" t="n">
-        <v>7.096177586197572</v>
+        <v>5.68056893135881</v>
       </c>
       <c r="E11" t="n">
-        <v>18.37863778963598</v>
+        <v>13.82094600561617</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.599919491750369</v>
+        <v>1.063978891954523</v>
       </c>
       <c r="C12" t="n">
-        <v>10.63906362815155</v>
+        <v>8.385774730410896</v>
       </c>
       <c r="D12" t="n">
-        <v>7.62278280835928</v>
+        <v>6.112047047375282</v>
       </c>
       <c r="E12" t="n">
-        <v>20.8617659282612</v>
+        <v>15.5618006697407</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.941926338698668</v>
+        <v>0.8471108240864028</v>
       </c>
       <c r="C13" t="n">
-        <v>12.26586399735429</v>
+        <v>7.88678182477337</v>
       </c>
       <c r="D13" t="n">
-        <v>8.112249656309492</v>
+        <v>5.574481274437899</v>
       </c>
       <c r="E13" t="n">
-        <v>23.32003999236245</v>
+        <v>14.30837392329767</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.696381493122149</v>
+        <v>0.9290965748680541</v>
       </c>
       <c r="C14" t="n">
-        <v>8.61117418582892</v>
+        <v>9.14924065009547</v>
       </c>
       <c r="D14" t="n">
-        <v>6.171256251418408</v>
+        <v>5.93041390461258</v>
       </c>
       <c r="E14" t="n">
-        <v>16.47881193036948</v>
+        <v>16.0087511295761</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.742376373066112</v>
+        <v>0.9116312832095033</v>
       </c>
       <c r="C15" t="n">
-        <v>9.342389693428988</v>
+        <v>9.786748339325179</v>
       </c>
       <c r="D15" t="n">
-        <v>6.199550220254801</v>
+        <v>5.981346975508904</v>
       </c>
       <c r="E15" t="n">
-        <v>17.2843162867499</v>
+        <v>16.67972659804359</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.040150269241212</v>
+        <v>1.009963133266864</v>
       </c>
       <c r="C16" t="n">
-        <v>11.09925666260978</v>
+        <v>11.44299598629772</v>
       </c>
       <c r="D16" t="n">
-        <v>6.657476619423683</v>
+        <v>6.389371138870922</v>
       </c>
       <c r="E16" t="n">
-        <v>19.79688355127468</v>
+        <v>18.8423302584355</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.649993914096487</v>
+        <v>0.6150845716647118</v>
       </c>
       <c r="C17" t="n">
-        <v>10.29493040347445</v>
+        <v>8.621796695988872</v>
       </c>
       <c r="D17" t="n">
-        <v>6.174073867329596</v>
+        <v>5.311039095480309</v>
       </c>
       <c r="E17" t="n">
-        <v>18.11899818490054</v>
+        <v>14.54792036313389</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.892524866953619</v>
+        <v>0.4921304891848412</v>
       </c>
       <c r="C18" t="n">
-        <v>12.08751335413575</v>
+        <v>7.65075004171835</v>
       </c>
       <c r="D18" t="n">
-        <v>6.578200492305752</v>
+        <v>4.839908189689308</v>
       </c>
       <c r="E18" t="n">
-        <v>20.55823871339512</v>
+        <v>12.9827887205925</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.90624969985899</v>
+        <v>0.5837962723303659</v>
       </c>
       <c r="C19" t="n">
-        <v>12.99559071065588</v>
+        <v>9.520174385191043</v>
       </c>
       <c r="D19" t="n">
-        <v>6.657142825204239</v>
+        <v>5.31012607011536</v>
       </c>
       <c r="E19" t="n">
-        <v>21.55898323571911</v>
+        <v>15.41409672763677</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.122636711352029</v>
+        <v>0.6718786763553897</v>
       </c>
       <c r="C20" t="n">
-        <v>15.01217903499517</v>
+        <v>11.48350289657494</v>
       </c>
       <c r="D20" t="n">
-        <v>7.10698944076717</v>
+        <v>5.821282829808505</v>
       </c>
       <c r="E20" t="n">
-        <v>24.24180518711437</v>
+        <v>17.97666440273884</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.262949699174224</v>
+        <v>0.7504872150344317</v>
       </c>
       <c r="C21" t="n">
-        <v>11.09820619256624</v>
+        <v>13.4489716179541</v>
       </c>
       <c r="D21" t="n">
-        <v>5.932338130112904</v>
+        <v>6.277805329760314</v>
       </c>
       <c r="E21" t="n">
-        <v>18.29349402185337</v>
+        <v>20.47726416274885</v>
       </c>
     </row>
   </sheetData>
